--- a/public/spreadsheets/Week 1;.xlsx
+++ b/public/spreadsheets/Week 1;.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nickstigsell/dev/football-pool/public/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2672875-F45A-974D-8F3E-442CF22B6DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67381E66-E7B6-D44F-8E46-3539D43B33A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="860" windowWidth="23920" windowHeight="20080" xr2:uid="{E5A893EA-7D07-4363-8558-9984C8A0723C}"/>
+    <workbookView xWindow="1540" yWindow="760" windowWidth="17280" windowHeight="13040" xr2:uid="{E5A893EA-7D07-4363-8558-9984C8A0723C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="45">
   <si>
     <t>Rick</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Nick</t>
   </si>
   <si>
+    <t>POINTS</t>
+  </si>
+  <si>
     <t>Adam</t>
   </si>
   <si>
@@ -66,122 +69,117 @@
     <t>Connor</t>
   </si>
   <si>
+    <t>Jake</t>
+  </si>
+  <si>
     <t>WK 1</t>
   </si>
   <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>SEAT</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>RAMS</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>JETS</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>INDY</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>PITT</t>
+  </si>
+  <si>
+    <t>CHIC</t>
+  </si>
+  <si>
+    <t>CAR</t>
+  </si>
+  <si>
+    <t>CLEV</t>
+  </si>
+  <si>
+    <t>JAX</t>
+  </si>
+  <si>
+    <t>BUF</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>WASH</t>
+  </si>
+  <si>
+    <t>PHIL</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
     <t>DAL</t>
   </si>
   <si>
-    <t>PHIL</t>
+    <t>GIA</t>
+  </si>
+  <si>
+    <t>DEN</t>
   </si>
   <si>
     <t>KC</t>
   </si>
   <si>
-    <t>CHRGERS</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>CLEV</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>INDY</t>
-  </si>
-  <si>
-    <t>LV</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>PITT</t>
-  </si>
-  <si>
-    <t>JETS</t>
-  </si>
-  <si>
-    <t>GIA</t>
-  </si>
-  <si>
-    <t>WASH</t>
-  </si>
-  <si>
-    <t>CAR</t>
-  </si>
-  <si>
-    <t>JAX</t>
-  </si>
-  <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>SEAT</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>GB</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>RAMS</t>
-  </si>
-  <si>
     <t>BALT</t>
-  </si>
-  <si>
-    <t>BUF</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>CHIC</t>
-  </si>
-  <si>
-    <t>POINTS</t>
-  </si>
-  <si>
-    <t>Phil</t>
-  </si>
-  <si>
-    <t>Jake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEN </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-409]General"/>
+    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[Red]&quot;-&quot;[$$-409]#,##0.00"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,12 +207,34 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -226,7 +246,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -314,75 +334,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -407,46 +358,28 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -467,44 +400,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="8">
+    <cellStyle name="Excel Built-in Normal" xfId="3" xr:uid="{E8341A5A-22B0-4265-932E-574D39AFE0BA}"/>
+    <cellStyle name="Heading" xfId="4" xr:uid="{53649DC6-4802-4EF4-93DC-057903678513}"/>
+    <cellStyle name="Heading1" xfId="5" xr:uid="{E3217A1C-4C85-43EB-85E7-ACFF5127338C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{CF63ED34-52FD-4E9C-8EF5-C389BA5F3AAF}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{01D04351-12FC-43E7-91F1-7099BAE97302}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{0C73BCB9-C6D4-4EC1-97F6-30906FD33FB7}"/>
+    <cellStyle name="Result" xfId="6" xr:uid="{2CEE3C39-E6F6-411E-9153-63DCCE7638E2}"/>
+    <cellStyle name="Result2" xfId="7" xr:uid="{AE025CE6-F264-49EA-B0A7-346A8C8D535F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -819,7 +734,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="10" width="7.83203125" customWidth="1"/>
@@ -827,21 +742,21 @@
     <col min="12" max="14" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -853,24 +768,24 @@
         <v>1</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -881,591 +796,576 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="20"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="20"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="21" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="14"/>
+        <v>17</v>
+      </c>
+      <c r="B6" s="13"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="13"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="21"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="B8" s="13"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="21"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-    </row>
-    <row r="9" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-    </row>
-    <row r="10" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="B10" s="13"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="21"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-    </row>
-    <row r="11" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="B12" s="13"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="21"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-    </row>
-    <row r="13" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>21</v>
+        <v>44</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-    </row>
-    <row r="14" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="14"/>
+        <v>24</v>
+      </c>
+      <c r="B14" s="13"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="21"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-    </row>
-    <row r="15" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>23</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="21" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row r="16" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="B16" s="13"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="13"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="21"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>25</v>
+      <c r="D17" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="21" t="s">
         <v>26</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="14"/>
+        <v>28</v>
+      </c>
+      <c r="B18" s="13"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="13"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="21"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="B20" s="13"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="13"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="21"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="C21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>30</v>
@@ -1473,55 +1373,53 @@
       <c r="J21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K21" s="19" t="s">
+      <c r="K21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L21" s="21" t="s">
-        <v>29</v>
+      <c r="L21" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="B22" s="13"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="13"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="21"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="E23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="F23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>32</v>
@@ -1530,60 +1428,58 @@
         <v>32</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B24" s="13"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="D24" s="13"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="21"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>34</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>33</v>
+      <c r="D25" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>34</v>
@@ -1592,178 +1488,172 @@
         <v>34</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="L25" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-    </row>
-    <row r="26" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="B26" s="13"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="21"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-    </row>
-    <row r="28" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B28" s="13"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="21"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="L29" s="21" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-    </row>
-    <row r="30" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="14"/>
+        <v>40</v>
+      </c>
+      <c r="B30" s="13"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="21"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>39</v>
+      <c r="D31" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>40</v>
@@ -1772,137 +1662,132 @@
         <v>40</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>40</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K31" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="L31" s="21" t="s">
+      <c r="L31" s="4" t="s">
         <v>40</v>
       </c>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B32" s="13"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="21"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="C33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K33" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="L33" s="21" t="s">
-        <v>41</v>
+      <c r="K33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="1:16" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B34" s="13">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C34" s="3">
+        <v>45</v>
+      </c>
+      <c r="D34" s="13">
         <v>44</v>
-      </c>
-      <c r="D34" s="3">
-        <v>46</v>
       </c>
       <c r="E34" s="3">
         <v>42</v>
       </c>
       <c r="F34" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H34" s="3">
         <v>48</v>
       </c>
       <c r="I34" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J34" s="3">
-        <v>44</v>
-      </c>
-      <c r="K34" s="18">
+        <v>41</v>
+      </c>
+      <c r="K34" s="3">
         <v>42</v>
       </c>
-      <c r="L34" s="21">
-        <v>48</v>
+      <c r="L34" s="3">
+        <v>42</v>
       </c>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5"/>
-      <c r="B35" s="16"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B35" s="11"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1914,13 +1799,11 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A36" s="5"/>
-      <c r="B36" s="16"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="D36" s="11"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1932,11 +1815,9 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A37" s="5"/>
-      <c r="B37" s="16"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1950,10 +1831,9 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B38" s="17"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1968,9 +1848,6 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B39" s="16"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
